--- a/InputData/elec/STfESCE/STfESCE Smoothing Time for Electricity Sector Capital Expenditures.xlsx
+++ b/InputData/elec/STfESCE/STfESCE Smoothing Time for Electricity Sector Capital Expenditures.xlsx
@@ -1,61 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\elec\STfESCE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\STfESCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AACA472-9A57-4B97-8AEB-060957311C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7D789D-91F1-4138-BEC9-487F1887F133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12420" yWindow="795" windowWidth="33855" windowHeight="21540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="STfESCE" sheetId="17" r:id="rId2"/>
+    <sheet name="STfESCE" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>STfESCE Smoothing Time for Electricity Sector Capital Expenditures</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>None needed</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>None needed</t>
+    <t xml:space="preserve">This variable is used with Vensim's DEPRECIATE STRAIGHTLINE function to smooth capital costs in the power sector </t>
+  </si>
+  <si>
+    <t>over a set number of years.</t>
   </si>
   <si>
     <t>Smoothing Time (years)</t>
-  </si>
-  <si>
-    <t>STfESCE Smoothing Time for Electricity Sector Capital Expenditures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This variable is used with Vensim's DEPRECIATE STRAIGHTLINE function to smooth capital costs in the power sector </t>
-  </si>
-  <si>
-    <t>over a set number of years.</t>
   </si>
   <si>
     <t>capital expenditures</t>
@@ -135,28 +124,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -434,109 +419,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="93" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
+      <c r="A17" s="3"/>
       <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -544,7 +503,6 @@
       <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
       <c r="B19" s="3"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -560,7 +518,6 @@
       <c r="B22" s="3"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
       <c r="B23" s="3"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -573,12 +530,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AA279E-4463-4946-87ED-B3052716FB44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
@@ -589,16 +546,16 @@
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5">
         <v>3</v>
       </c>
     </row>

--- a/InputData/elec/STfESCE/STfESCE Smoothing Time for Electricity Sector Capital Expenditures.xlsx
+++ b/InputData/elec/STfESCE/STfESCE Smoothing Time for Electricity Sector Capital Expenditures.xlsx
@@ -1,50 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\STfESCE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\elec\STfESCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7D789D-91F1-4138-BEC9-487F1887F133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AACA472-9A57-4B97-8AEB-060957311C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12420" yWindow="795" windowWidth="33855" windowHeight="21540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="STfESCE" sheetId="2" r:id="rId2"/>
+    <sheet name="STfESCE" sheetId="17" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>None needed</t>
+  </si>
+  <si>
+    <t>Smoothing Time (years)</t>
+  </si>
   <si>
     <t>STfESCE Smoothing Time for Electricity Sector Capital Expenditures</t>
   </si>
   <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>None needed</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t xml:space="preserve">This variable is used with Vensim's DEPRECIATE STRAIGHTLINE function to smooth capital costs in the power sector </t>
   </si>
   <si>
     <t>over a set number of years.</t>
-  </si>
-  <si>
-    <t>Smoothing Time (years)</t>
   </si>
   <si>
     <t>capital expenditures</t>
@@ -124,24 +135,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -419,83 +434,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="93" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="6"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
+      <c r="A17" s="6"/>
       <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -503,6 +544,7 @@
       <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
       <c r="B19" s="3"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -518,6 +560,7 @@
       <c r="B22" s="3"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
       <c r="B23" s="3"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -530,12 +573,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AA279E-4463-4946-87ED-B3052716FB44}">
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
@@ -546,16 +589,16 @@
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="5">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7">
         <v>3</v>
       </c>
     </row>
